--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260624_211639.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260624_211639.xlsx
@@ -6340,7 +6340,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260624_211639.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260624_211639.xlsx
@@ -6340,7 +6340,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
